--- a/research/traditional_assets/database/data/japan/japan_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/japan/japan_insurance_life.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0296</v>
+        <v>-0.00381</v>
       </c>
       <c r="E2">
-        <v>0.1052</v>
+        <v>0.1014</v>
       </c>
       <c r="F2">
-        <v>-0.0672</v>
+        <v>-0.0708</v>
       </c>
       <c r="G2">
-        <v>0.04055363033221468</v>
+        <v>0.04360246709304796</v>
       </c>
       <c r="H2">
-        <v>0.04055363033221468</v>
+        <v>0.04360246709304796</v>
       </c>
       <c r="I2">
-        <v>0.04030015351033732</v>
+        <v>0.02819205418114052</v>
       </c>
       <c r="J2">
-        <v>0.03190216381315229</v>
+        <v>0.02391081841284039</v>
       </c>
       <c r="K2">
-        <v>10677.3</v>
+        <v>5099.7</v>
       </c>
       <c r="L2">
-        <v>0.04637896329836078</v>
+        <v>0.02936020352999494</v>
       </c>
       <c r="M2">
-        <v>9452.098400000001</v>
+        <v>4705.949</v>
       </c>
       <c r="N2">
-        <v>0.1453057954148905</v>
+        <v>0.06891225526805195</v>
       </c>
       <c r="O2">
-        <v>0.8852517396720144</v>
+        <v>0.9227893797674372</v>
       </c>
       <c r="P2">
-        <v>2976.2984</v>
+        <v>2155.793</v>
       </c>
       <c r="Q2">
-        <v>0.04575422177196821</v>
+        <v>0.03156867138192095</v>
       </c>
       <c r="R2">
-        <v>0.2787500959980519</v>
+        <v>0.4227293762378179</v>
       </c>
       <c r="S2">
-        <v>6475.8</v>
+        <v>2550.156</v>
       </c>
       <c r="T2">
-        <v>0.6851177088888537</v>
+        <v>0.5419004753345181</v>
       </c>
       <c r="U2">
-        <v>602040</v>
+        <v>457712.3</v>
       </c>
       <c r="V2">
-        <v>9.255077271686112</v>
+        <v>6.702577281846271</v>
       </c>
       <c r="W2">
-        <v>0.05335813216047077</v>
+        <v>0.02536011630539621</v>
       </c>
       <c r="X2">
-        <v>0.07301237056307169</v>
+        <v>0.1084724837129108</v>
       </c>
       <c r="Y2">
-        <v>-0.01965423840260092</v>
+        <v>-0.08311236740751461</v>
       </c>
       <c r="Z2">
-        <v>-2.615367210817758</v>
+        <v>1.805570128575021</v>
       </c>
       <c r="AA2">
-        <v>0.04702128910246649</v>
+        <v>0.05671081262715132</v>
       </c>
       <c r="AB2">
-        <v>0.05961399877984084</v>
+        <v>0.09402315486712791</v>
       </c>
       <c r="AC2">
-        <v>-0.007003668023698451</v>
+        <v>-0.03731234223997659</v>
       </c>
       <c r="AD2">
-        <v>287854.1</v>
+        <v>210130.9</v>
       </c>
       <c r="AE2">
-        <v>720.4553953252861</v>
+        <v>562.4594172236265</v>
       </c>
       <c r="AF2">
-        <v>288574.5553953253</v>
+        <v>210693.3594172236</v>
       </c>
       <c r="AG2">
-        <v>-313465.4446046747</v>
+        <v>-247018.9405827764</v>
       </c>
       <c r="AH2">
-        <v>0.8160485345461403</v>
+        <v>0.7552210822840147</v>
       </c>
       <c r="AI2">
-        <v>0.5590667070904929</v>
+        <v>0.6080757538258487</v>
       </c>
       <c r="AJ2">
-        <v>1.26185820107143</v>
+        <v>1.382079240765891</v>
       </c>
       <c r="AK2">
-        <v>3.650548304061526</v>
+        <v>2.220987090027216</v>
       </c>
       <c r="AL2">
-        <v>260.4</v>
+        <v>220.407</v>
       </c>
       <c r="AM2">
-        <v>260.4</v>
+        <v>220.407</v>
       </c>
       <c r="AN2">
-        <v>26.42672927590048</v>
+        <v>34.16156581003273</v>
       </c>
       <c r="AO2">
-        <v>35.65015360983103</v>
+        <v>22.08459803908224</v>
       </c>
       <c r="AP2">
-        <v>-28.77800400243568</v>
+        <v>-40.15855733280103</v>
       </c>
       <c r="AQ2">
-        <v>35.65015360983103</v>
+        <v>22.08459803908224</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>T&amp;D Holdings, Inc. (TSE:8795)</t>
+          <t>Japan Post Holdings Co., Ltd. (TSE:6178)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,124 +725,109 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.03700000000000001</v>
+        <v>-0.0344</v>
       </c>
       <c r="E3">
-        <v>0.0153</v>
+        <v>2.154</v>
       </c>
       <c r="F3">
-        <v>-0.13</v>
+        <v>0.0334</v>
       </c>
       <c r="G3">
-        <v>0.1230684804898478</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.1230684804898478</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.07874878235258129</v>
+        <v>0.0002560385425456858</v>
       </c>
       <c r="J3">
-        <v>0.05550719902023187</v>
+        <v>0.000188739482237696</v>
       </c>
       <c r="K3">
-        <v>700</v>
+        <v>3057.9</v>
       </c>
       <c r="L3">
-        <v>0.03369629051978935</v>
+        <v>0.04053151302273179</v>
       </c>
       <c r="M3">
-        <v>485.6072</v>
+        <v>2571.6128</v>
       </c>
       <c r="N3">
-        <v>0.06558094183424042</v>
+        <v>0.08691375248833146</v>
       </c>
       <c r="O3">
-        <v>0.6937245714285715</v>
+        <v>0.840973478531018</v>
       </c>
       <c r="P3">
-        <v>269.9072</v>
+        <v>1216.8128</v>
       </c>
       <c r="Q3">
-        <v>0.03645079476548679</v>
+        <v>0.04112507393174959</v>
       </c>
       <c r="R3">
-        <v>0.3855817142857144</v>
+        <v>0.397924327152621</v>
       </c>
       <c r="S3">
-        <v>215.7</v>
+        <v>1354.8</v>
       </c>
       <c r="T3">
-        <v>0.4441861652792627</v>
+        <v>0.5268289223012111</v>
       </c>
       <c r="U3">
-        <v>10246.6</v>
+        <v>428806.3</v>
       </c>
       <c r="V3">
-        <v>1.383796777722258</v>
+        <v>14.49252571135017</v>
       </c>
       <c r="W3">
-        <v>0.05335813216047077</v>
+        <v>0.02536011630539621</v>
       </c>
       <c r="X3">
-        <v>0.06833778115611526</v>
+        <v>0.3495137700438335</v>
       </c>
       <c r="Y3">
-        <v>-0.01497964899564449</v>
-      </c>
-      <c r="Z3">
-        <v>3.751189936823291</v>
-      </c>
-      <c r="AA3">
-        <v>0.2082180463859414</v>
+        <v>-0.3241536537384373</v>
       </c>
       <c r="AB3">
-        <v>0.06042810913656957</v>
-      </c>
-      <c r="AC3">
-        <v>0.1477899372493719</v>
+        <v>0.08825869074456744</v>
       </c>
       <c r="AD3">
-        <v>1461.3</v>
+        <v>170389.4</v>
       </c>
       <c r="AE3">
-        <v>0.122725819735693</v>
+        <v>230.4158607882037</v>
       </c>
       <c r="AF3">
-        <v>1461.422725819736</v>
+        <v>170619.8158607882</v>
       </c>
       <c r="AG3">
-        <v>-8785.177274180265</v>
+        <v>-258186.4841392118</v>
       </c>
       <c r="AH3">
-        <v>0.1648322238495313</v>
+        <v>0.8522131361650371</v>
       </c>
       <c r="AI3">
-        <v>0.0907720335499515</v>
+        <v>0.6463187239439495</v>
       </c>
       <c r="AJ3">
-        <v>6.363869538813632</v>
+        <v>1.129432673425992</v>
       </c>
       <c r="AK3">
-        <v>-1.500887220078906</v>
+        <v>1.566483206961751</v>
       </c>
       <c r="AL3">
-        <v>14.4</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>14.4</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.8053298474100266</v>
-      </c>
-      <c r="AO3">
-        <v>113.6041666666667</v>
+        <v>2605.34250764526</v>
       </c>
       <c r="AP3">
-        <v>-4.841555788466178</v>
-      </c>
-      <c r="AQ3">
-        <v>113.6041666666667</v>
+        <v>-3947.805567877856</v>
       </c>
     </row>
     <row r="4">
@@ -853,7 +838,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dai-ichi Life Holdings, Inc. (TSE:8750)</t>
+          <t>T&amp;D Holdings, Inc. (TSE:8795)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -862,124 +847,124 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0296</v>
+        <v>-0.00381</v>
       </c>
       <c r="E4">
-        <v>0.252</v>
+        <v>0.143</v>
       </c>
       <c r="F4">
-        <v>-0.05429999999999999</v>
+        <v>-0.126</v>
       </c>
       <c r="G4">
-        <v>0.04527920711733068</v>
+        <v>0.05319597427583722</v>
       </c>
       <c r="H4">
-        <v>0.04527920711733068</v>
+        <v>0.05319597427583722</v>
       </c>
       <c r="I4">
-        <v>0.06470804648750808</v>
+        <v>0.04938962470472639</v>
       </c>
       <c r="J4">
-        <v>0.04917677663401269</v>
+        <v>0.04938962470472639</v>
       </c>
       <c r="K4">
-        <v>4114.3</v>
+        <v>-1141.3</v>
       </c>
       <c r="L4">
-        <v>0.05836954563317259</v>
+        <v>-0.08748208276803028</v>
       </c>
       <c r="M4">
-        <v>1388.536</v>
+        <v>384.5252</v>
       </c>
       <c r="N4">
-        <v>0.06510329047927157</v>
+        <v>0.04796851375963673</v>
       </c>
       <c r="O4">
-        <v>0.3374902170478575</v>
+        <v>-0.3369186015946727</v>
       </c>
       <c r="P4">
-        <v>587.1360000000001</v>
+        <v>107.8252</v>
       </c>
       <c r="Q4">
-        <v>0.02752862407516809</v>
+        <v>0.01345091190339562</v>
       </c>
       <c r="R4">
-        <v>0.1427061711591279</v>
+        <v>-0.09447577324104092</v>
       </c>
       <c r="S4">
-        <v>801.4</v>
+        <v>276.7</v>
       </c>
       <c r="T4">
-        <v>0.5771546434518082</v>
+        <v>0.7195887291652147</v>
       </c>
       <c r="U4">
-        <v>17486.2</v>
+        <v>6765.8</v>
       </c>
       <c r="V4">
-        <v>0.8198629045113981</v>
+        <v>0.8440158678675682</v>
       </c>
       <c r="W4">
-        <v>0.09979068283963104</v>
+        <v>-0.07833165180746872</v>
       </c>
       <c r="X4">
-        <v>0.07301237056307169</v>
+        <v>0.102214755052536</v>
       </c>
       <c r="Y4">
-        <v>0.02677831227655934</v>
+        <v>-0.1805464068600047</v>
       </c>
       <c r="Z4">
-        <v>1.82662601307513</v>
+        <v>2.255142320714539</v>
       </c>
       <c r="AA4">
-        <v>0.08982757943887282</v>
+        <v>0.1113806328758368</v>
       </c>
       <c r="AB4">
-        <v>0.05961399877984084</v>
+        <v>0.0949109772334443</v>
       </c>
       <c r="AC4">
-        <v>0.03021358065903198</v>
+        <v>0.01646965564239247</v>
       </c>
       <c r="AD4">
-        <v>7197.2</v>
+        <v>1126.6</v>
       </c>
       <c r="AE4">
-        <v>81.08728215184516</v>
+        <v>0.2450856983451643</v>
       </c>
       <c r="AF4">
-        <v>7278.287282151845</v>
+        <v>1126.845085698345</v>
       </c>
       <c r="AG4">
-        <v>-10207.91271784816</v>
+        <v>-5638.954914301656</v>
       </c>
       <c r="AH4">
-        <v>0.2544278579318235</v>
+        <v>0.1232461477698463</v>
       </c>
       <c r="AI4">
-        <v>0.1400055988997319</v>
+        <v>0.1417656812638205</v>
       </c>
       <c r="AJ4">
-        <v>-0.9179540473052294</v>
+        <v>-2.37205450469788</v>
       </c>
       <c r="AK4">
-        <v>-0.2958859253287852</v>
+        <v>-4.767281009560479</v>
       </c>
       <c r="AL4">
-        <v>223.7</v>
+        <v>12.2</v>
       </c>
       <c r="AM4">
-        <v>223.7</v>
+        <v>12.2</v>
       </c>
       <c r="AN4">
-        <v>1.348497339428914</v>
+        <v>1.42898637858626</v>
       </c>
       <c r="AO4">
-        <v>20.39427805096111</v>
+        <v>52.81147540983606</v>
       </c>
       <c r="AP4">
-        <v>-1.912597001770246</v>
+        <v>-7.15248514290708</v>
       </c>
       <c r="AQ4">
-        <v>20.39427805096111</v>
+        <v>52.81147540983606</v>
       </c>
     </row>
     <row r="5">
@@ -990,7 +975,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Japan Post Insurance Co., Ltd. (TSE:7181)</t>
+          <t>Dai-ichi Life Holdings, Inc. (TSE:8750)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -999,124 +984,124 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.115</v>
+        <v>0.0683</v>
       </c>
       <c r="E5">
-        <v>0.142</v>
+        <v>0.05980000000000001</v>
       </c>
       <c r="F5">
-        <v>-0.0801</v>
+        <v>-0.0489</v>
       </c>
       <c r="G5">
-        <v>0.1091228727292499</v>
+        <v>0.06084439843802051</v>
       </c>
       <c r="H5">
-        <v>0.1091228727292499</v>
+        <v>0.06084439843802051</v>
       </c>
       <c r="I5">
-        <v>0.09399136353490609</v>
+        <v>0.03678412611673629</v>
       </c>
       <c r="J5">
-        <v>0.07091755939247921</v>
+        <v>0.0318341148323688</v>
       </c>
       <c r="K5">
-        <v>1371.4</v>
+        <v>2343.6</v>
       </c>
       <c r="L5">
-        <v>0.04142476544895456</v>
+        <v>0.0380842188396306</v>
       </c>
       <c r="M5">
-        <v>3648.86</v>
+        <v>1352.7352</v>
       </c>
       <c r="N5">
-        <v>0.5684025235610251</v>
+        <v>0.05814264714731495</v>
       </c>
       <c r="O5">
-        <v>2.660682514219046</v>
+        <v>0.5772039597200888</v>
       </c>
       <c r="P5">
-        <v>431.46</v>
+        <v>588.2352</v>
       </c>
       <c r="Q5">
-        <v>0.0672108419658852</v>
+        <v>0.02528325696945731</v>
       </c>
       <c r="R5">
-        <v>0.3146128044334257</v>
+        <v>0.2509964157706093</v>
       </c>
       <c r="S5">
-        <v>3217.4</v>
+        <v>764.5000000000001</v>
       </c>
       <c r="T5">
-        <v>0.8817548494598313</v>
+        <v>0.5651512579845634</v>
       </c>
       <c r="U5">
-        <v>10881.4</v>
+        <v>13970.4</v>
       </c>
       <c r="V5">
-        <v>1.69505413194174</v>
+        <v>0.6004693584574784</v>
       </c>
       <c r="W5">
-        <v>0.05814145747923671</v>
+        <v>0.05242085202897059</v>
       </c>
       <c r="X5">
-        <v>0.278426722716937</v>
+        <v>0.1084724837129108</v>
       </c>
       <c r="Y5">
-        <v>-0.2202852652377003</v>
+        <v>-0.05605163168394023</v>
       </c>
       <c r="Z5">
-        <v>0.663041558469835</v>
+        <v>1.781447762118644</v>
       </c>
       <c r="AA5">
-        <v>0.04702128910246649</v>
+        <v>0.05671081262715132</v>
       </c>
       <c r="AB5">
-        <v>0.05402495712616494</v>
+        <v>0.09402315486712791</v>
       </c>
       <c r="AC5">
-        <v>-0.007003668023698451</v>
+        <v>-0.03731234223997659</v>
       </c>
       <c r="AD5">
-        <v>42475.8</v>
+        <v>6457.6</v>
       </c>
       <c r="AE5">
-        <v>304.2035854305302</v>
+        <v>125.0209795828195</v>
       </c>
       <c r="AF5">
-        <v>42780.00358543053</v>
+        <v>6582.62097958282</v>
       </c>
       <c r="AG5">
-        <v>31898.60358543053</v>
+        <v>-7387.77902041718</v>
       </c>
       <c r="AH5">
-        <v>0.8695210412265011</v>
+        <v>0.2205349818700802</v>
       </c>
       <c r="AI5">
-        <v>0.6417035486392231</v>
+        <v>0.2439162218504418</v>
       </c>
       <c r="AJ5">
-        <v>0.8324682226069025</v>
+        <v>-0.4652833643384748</v>
       </c>
       <c r="AK5">
-        <v>0.5718142639895422</v>
+        <v>-0.5675563205490096</v>
       </c>
       <c r="AL5">
-        <v>22.3</v>
+        <v>193.5</v>
       </c>
       <c r="AM5">
-        <v>22.3</v>
+        <v>193.5</v>
       </c>
       <c r="AN5">
-        <v>11.47746433203632</v>
+        <v>2.169746656810699</v>
       </c>
       <c r="AO5">
-        <v>139.7130044843049</v>
+        <v>11.71369509043928</v>
       </c>
       <c r="AP5">
-        <v>8.619380562427185</v>
+        <v>-2.482285807545588</v>
       </c>
       <c r="AQ5">
-        <v>139.7130044843049</v>
+        <v>11.71369509043928</v>
       </c>
     </row>
     <row r="6">
@@ -1127,7 +1112,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Japan Post Holdings Co., Ltd. (TSE:6178)</t>
+          <t>Japan Post Insurance Co., Ltd. (TSE:7181)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1136,118 +1121,124 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.0288</v>
+        <v>-0.09960000000000001</v>
       </c>
       <c r="E6">
-        <v>0.0684</v>
+        <v>0.0527</v>
       </c>
       <c r="F6">
-        <v>0.0273</v>
+        <v>-0.09269999999999999</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>0.1343724210687517</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.1343724210687517</v>
       </c>
       <c r="I6">
-        <v>-3.864385013314713e-06</v>
+        <v>0.08502473654570604</v>
       </c>
       <c r="J6">
-        <v>-2.854678356864428e-06</v>
+        <v>0.05425584061829693</v>
       </c>
       <c r="K6">
-        <v>4522.5</v>
+        <v>869.6</v>
       </c>
       <c r="L6">
-        <v>0.04279720041486551</v>
+        <v>0.03699197713099482</v>
       </c>
       <c r="M6">
-        <v>3929.0952</v>
+        <v>396.6197999999999</v>
       </c>
       <c r="N6">
-        <v>0.1339023003782844</v>
+        <v>0.0583521847874062</v>
       </c>
       <c r="O6">
-        <v>0.8687883250414594</v>
+        <v>0.4560945262189511</v>
       </c>
       <c r="P6">
-        <v>1687.7952</v>
+        <v>242.9198</v>
       </c>
       <c r="Q6">
-        <v>0.05751951743175544</v>
+        <v>0.03573926732381933</v>
       </c>
       <c r="R6">
-        <v>0.3731996019900498</v>
+        <v>0.2793465961361545</v>
       </c>
       <c r="S6">
-        <v>2241.3</v>
+        <v>153.7</v>
       </c>
       <c r="T6">
-        <v>0.5704366745809569</v>
+        <v>0.3875247781376522</v>
       </c>
       <c r="U6">
-        <v>563390.4</v>
+        <v>8147.7</v>
       </c>
       <c r="V6">
-        <v>19.20016358245578</v>
+        <v>1.198720023539797</v>
       </c>
       <c r="W6">
-        <v>0.03627637908395024</v>
+        <v>0.0364058058384932</v>
       </c>
       <c r="X6">
-        <v>0.32438659191074</v>
+        <v>0.3053379777792924</v>
       </c>
       <c r="Y6">
-        <v>-0.2881102128267898</v>
+        <v>-0.2689321719407992</v>
       </c>
       <c r="Z6">
-        <v>-0.5798931352554755</v>
+        <v>0.4221379932990163</v>
       </c>
       <c r="AA6">
-        <v>1.655408382508062e-06</v>
+        <v>0.02290345168335912</v>
       </c>
       <c r="AB6">
-        <v>0.05384021349088128</v>
+        <v>0.08849393436760383</v>
       </c>
       <c r="AC6">
-        <v>-0.05383855808249877</v>
+        <v>-0.06559048268424471</v>
       </c>
       <c r="AD6">
-        <v>236719.8</v>
+        <v>32157.3</v>
       </c>
       <c r="AE6">
-        <v>335.041801923175</v>
+        <v>206.7774911542581</v>
       </c>
       <c r="AF6">
-        <v>237054.8418019232</v>
+        <v>32364.07749115426</v>
       </c>
       <c r="AG6">
-        <v>-326335.5581980768</v>
+        <v>24216.37749115426</v>
       </c>
       <c r="AH6">
-        <v>0.8898527112625123</v>
+        <v>0.8264348063064579</v>
       </c>
       <c r="AI6">
-        <v>0.6218623955916192</v>
+        <v>0.6822096253360656</v>
       </c>
       <c r="AJ6">
-        <v>1.098800455398717</v>
+        <v>0.7808365115363954</v>
       </c>
       <c r="AK6">
-        <v>1.791192844098066</v>
+        <v>0.616312349554465</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>14.7</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>14.7</v>
       </c>
       <c r="AN6">
-        <v>3554.351351351352</v>
+        <v>13.69794683932527</v>
+      </c>
+      <c r="AO6">
+        <v>135.0952380952381</v>
       </c>
       <c r="AP6">
-        <v>-4899.93330627743</v>
+        <v>10.31537633802788</v>
+      </c>
+      <c r="AQ6">
+        <v>135.0952380952381</v>
       </c>
     </row>
     <row r="7">
@@ -1267,34 +1258,34 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.16</v>
+        <v>0.177</v>
       </c>
       <c r="G7">
-        <v>-0.1373534338358459</v>
+        <v>-0.148640101201771</v>
       </c>
       <c r="H7">
-        <v>-0.1373534338358459</v>
+        <v>-0.148640101201771</v>
       </c>
       <c r="I7">
-        <v>-0.1697375767727526</v>
+        <v>-0.1846932321315623</v>
       </c>
       <c r="J7">
-        <v>-0.1697375767727526</v>
+        <v>-0.1846932321315623</v>
       </c>
       <c r="K7">
-        <v>-30.9</v>
+        <v>-30.1</v>
       </c>
       <c r="L7">
-        <v>-0.1725293132328308</v>
+        <v>-0.1903858317520557</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>0.456</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.0007332368547998071</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>-0.01514950166112957</v>
       </c>
       <c r="P7">
         <v>-0</v>
@@ -1306,34 +1297,37 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>0.456</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
       </c>
       <c r="U7">
-        <v>35.4</v>
+        <v>22.1</v>
       </c>
       <c r="V7">
-        <v>0.06386433339346924</v>
+        <v>0.0355362598488503</v>
       </c>
       <c r="W7">
-        <v>-0.1859205776173285</v>
+        <v>-0.1376944190301921</v>
       </c>
       <c r="X7">
-        <v>0.06192585645353457</v>
+        <v>0.09603567656368478</v>
       </c>
       <c r="Y7">
-        <v>-0.2478464340708631</v>
+        <v>-0.2337300955938769</v>
       </c>
       <c r="Z7">
-        <v>1.227553118574366</v>
+        <v>0.8629912663755459</v>
       </c>
       <c r="AA7">
-        <v>-0.2083618917066484</v>
+        <v>-0.1593886462882096</v>
       </c>
       <c r="AB7">
-        <v>0.06192585645353457</v>
+        <v>0.09603567656368478</v>
       </c>
       <c r="AC7">
-        <v>-0.270287748160183</v>
+        <v>-0.2554243228518944</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1345,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>-35.4</v>
+        <v>-22.1</v>
       </c>
       <c r="AH7">
         <v>0</v>
@@ -1354,22 +1348,28 @@
         <v>0</v>
       </c>
       <c r="AJ7">
-        <v>-0.06822123723260744</v>
+        <v>-0.03684561520506836</v>
       </c>
       <c r="AK7">
-        <v>-0.1932314410480349</v>
+        <v>-0.2069288389513108</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="AN7">
         <v>-0</v>
       </c>
+      <c r="AO7">
+        <v>-4171.428571428572</v>
+      </c>
       <c r="AP7">
-        <v>1.330827067669173</v>
+        <v>0.8339622641509434</v>
+      </c>
+      <c r="AQ7">
+        <v>-4171.428571428572</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/japan/japan_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/japan/japan_insurance_life.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.00381</v>
+        <v>0.00484</v>
       </c>
       <c r="E2">
-        <v>0.1014</v>
+        <v>-0.06425</v>
       </c>
       <c r="F2">
-        <v>-0.0708</v>
+        <v>-0.03163</v>
       </c>
       <c r="G2">
-        <v>0.04360246709304796</v>
+        <v>0.07932358003442341</v>
       </c>
       <c r="H2">
-        <v>0.04360246709304796</v>
+        <v>0.07932358003442341</v>
       </c>
       <c r="I2">
-        <v>0.02819205418114052</v>
+        <v>0.04991875554126726</v>
       </c>
       <c r="J2">
-        <v>0.02391081841284039</v>
+        <v>0.03460100915741767</v>
       </c>
       <c r="K2">
-        <v>5099.7</v>
+        <v>4994.696</v>
       </c>
       <c r="L2">
-        <v>0.02936020352999494</v>
+        <v>0.02865574297188755</v>
       </c>
       <c r="M2">
-        <v>4705.949</v>
+        <v>5606.4524</v>
       </c>
       <c r="N2">
-        <v>0.06891225526805195</v>
+        <v>0.08443948364437068</v>
       </c>
       <c r="O2">
-        <v>0.9227893797674372</v>
+        <v>1.122481208065516</v>
       </c>
       <c r="P2">
-        <v>2155.793</v>
+        <v>2703.3524</v>
       </c>
       <c r="Q2">
-        <v>0.03156867138192095</v>
+        <v>0.0407155299784174</v>
       </c>
       <c r="R2">
-        <v>0.4227293762378179</v>
+        <v>0.5412446323059501</v>
       </c>
       <c r="S2">
-        <v>2550.156</v>
+        <v>2903.1</v>
       </c>
       <c r="T2">
-        <v>0.5419004753345181</v>
+        <v>0.5178140815036617</v>
       </c>
       <c r="U2">
-        <v>457712.3</v>
+        <v>462242.7</v>
       </c>
       <c r="V2">
-        <v>6.702577281846271</v>
+        <v>6.961895352287257</v>
       </c>
       <c r="W2">
-        <v>0.02536011630539621</v>
+        <v>0.04430220217564341</v>
       </c>
       <c r="X2">
-        <v>0.1084724837129108</v>
+        <v>0.09243527569871732</v>
       </c>
       <c r="Y2">
-        <v>-0.08311236740751461</v>
+        <v>-0.04813307352307391</v>
       </c>
       <c r="Z2">
-        <v>1.805570128575021</v>
+        <v>3.259302049140405</v>
       </c>
       <c r="AA2">
-        <v>0.05671081262715132</v>
+        <v>0.2452458346112759</v>
       </c>
       <c r="AB2">
-        <v>0.09402315486712791</v>
+        <v>0.0788251808446532</v>
       </c>
       <c r="AC2">
-        <v>-0.03731234223997659</v>
+        <v>0.1664206537666227</v>
       </c>
       <c r="AD2">
-        <v>210130.9</v>
+        <v>221808</v>
       </c>
       <c r="AE2">
-        <v>562.4594172236265</v>
+        <v>549.4045457855824</v>
       </c>
       <c r="AF2">
-        <v>210693.3594172236</v>
+        <v>222357.4045457856</v>
       </c>
       <c r="AG2">
-        <v>-247018.9405827764</v>
+        <v>-239885.2954542144</v>
       </c>
       <c r="AH2">
-        <v>0.7552210822840147</v>
+        <v>0.7700595873132613</v>
       </c>
       <c r="AI2">
-        <v>0.6080757538258487</v>
+        <v>0.6059441917442088</v>
       </c>
       <c r="AJ2">
-        <v>1.382079240765891</v>
+        <v>1.38271028824687</v>
       </c>
       <c r="AK2">
-        <v>2.220987090027216</v>
+        <v>2.517621881235102</v>
       </c>
       <c r="AL2">
-        <v>220.407</v>
+        <v>305.107</v>
       </c>
       <c r="AM2">
-        <v>220.407</v>
+        <v>305.107</v>
       </c>
       <c r="AN2">
-        <v>34.16156581003273</v>
+        <v>22.34640923886926</v>
       </c>
       <c r="AO2">
-        <v>22.08459803908224</v>
+        <v>28.42061965146653</v>
       </c>
       <c r="AP2">
-        <v>-40.15855733280103</v>
+        <v>-24.16763589503958</v>
       </c>
       <c r="AQ2">
-        <v>22.08459803908224</v>
+        <v>28.42061965146653</v>
       </c>
     </row>
     <row r="3">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0344</v>
+        <v>-0.0253</v>
       </c>
       <c r="E3">
-        <v>2.154</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="F3">
-        <v>0.0334</v>
+        <v>-0.00646</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -740,82 +740,82 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.0002560385425456858</v>
+        <v>0.0001834150485030975</v>
       </c>
       <c r="J3">
-        <v>0.000188739482237696</v>
+        <v>0.0001362604109074787</v>
       </c>
       <c r="K3">
-        <v>3057.9</v>
+        <v>2312.5</v>
       </c>
       <c r="L3">
-        <v>0.04053151302273179</v>
+        <v>0.03070796295656932</v>
       </c>
       <c r="M3">
-        <v>2571.6128</v>
+        <v>3410.677</v>
       </c>
       <c r="N3">
-        <v>0.08691375248833146</v>
+        <v>0.1152026116415985</v>
       </c>
       <c r="O3">
-        <v>0.840973478531018</v>
+        <v>1.474887351351351</v>
       </c>
       <c r="P3">
-        <v>1216.8128</v>
+        <v>1663.377</v>
       </c>
       <c r="Q3">
-        <v>0.04112507393174959</v>
+        <v>0.05618397008704346</v>
       </c>
       <c r="R3">
-        <v>0.397924327152621</v>
+        <v>0.7192981621621621</v>
       </c>
       <c r="S3">
-        <v>1354.8</v>
+        <v>1747.3</v>
       </c>
       <c r="T3">
-        <v>0.5268289223012111</v>
+        <v>0.5123029826629727</v>
       </c>
       <c r="U3">
-        <v>428806.3</v>
+        <v>436479.5</v>
       </c>
       <c r="V3">
-        <v>14.49252571135017</v>
+        <v>14.74299041745057</v>
       </c>
       <c r="W3">
-        <v>0.02536011630539621</v>
+        <v>0.02955936415091446</v>
       </c>
       <c r="X3">
-        <v>0.3495137700438335</v>
+        <v>0.2754123749866368</v>
       </c>
       <c r="Y3">
-        <v>-0.3241536537384373</v>
+        <v>-0.2458530108357223</v>
       </c>
       <c r="AB3">
-        <v>0.08825869074456744</v>
+        <v>0.06912640521345914</v>
       </c>
       <c r="AD3">
-        <v>170389.4</v>
+        <v>187388.2</v>
       </c>
       <c r="AE3">
-        <v>230.4158607882037</v>
+        <v>266.4385483720802</v>
       </c>
       <c r="AF3">
-        <v>170619.8158607882</v>
+        <v>187654.6385483721</v>
       </c>
       <c r="AG3">
-        <v>-258186.4841392118</v>
+        <v>-248824.8614516279</v>
       </c>
       <c r="AH3">
-        <v>0.8522131361650371</v>
+        <v>0.8637308910407199</v>
       </c>
       <c r="AI3">
-        <v>0.6463187239439495</v>
+        <v>0.6562811830809898</v>
       </c>
       <c r="AJ3">
-        <v>1.129432673425992</v>
+        <v>1.135051730032635</v>
       </c>
       <c r="AK3">
-        <v>1.566483206961751</v>
+        <v>1.652847323334442</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -824,10 +824,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>2605.34250764526</v>
+        <v>2792.670640834576</v>
       </c>
       <c r="AP3">
-        <v>-3947.805567877856</v>
+        <v>-3708.269172155409</v>
       </c>
     </row>
     <row r="4">
@@ -847,124 +847,124 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.00381</v>
+        <v>0.00484</v>
       </c>
       <c r="E4">
-        <v>0.143</v>
+        <v>-0.05599999999999999</v>
       </c>
       <c r="F4">
-        <v>-0.126</v>
+        <v>1.167</v>
       </c>
       <c r="G4">
-        <v>0.05319597427583722</v>
+        <v>0.1345560411634109</v>
       </c>
       <c r="H4">
-        <v>0.05319597427583722</v>
+        <v>0.1345560411634109</v>
       </c>
       <c r="I4">
-        <v>0.04938962470472639</v>
+        <v>0.1215320730807026</v>
       </c>
       <c r="J4">
-        <v>0.04938962470472639</v>
+        <v>0.08378251656187874</v>
       </c>
       <c r="K4">
-        <v>-1141.3</v>
+        <v>396.4</v>
       </c>
       <c r="L4">
-        <v>-0.08748208276803028</v>
+        <v>0.02767499336749654</v>
       </c>
       <c r="M4">
-        <v>384.5252</v>
+        <v>500.1054</v>
       </c>
       <c r="N4">
-        <v>0.04796851375963673</v>
+        <v>0.05841329206330666</v>
       </c>
       <c r="O4">
-        <v>-0.3369186015946727</v>
+        <v>1.261618062563068</v>
       </c>
       <c r="P4">
-        <v>107.8252</v>
+        <v>238.1054</v>
       </c>
       <c r="Q4">
-        <v>0.01345091190339562</v>
+        <v>0.02781117794778953</v>
       </c>
       <c r="R4">
-        <v>-0.09447577324104092</v>
+        <v>0.6006695257315844</v>
       </c>
       <c r="S4">
-        <v>276.7</v>
+        <v>262</v>
       </c>
       <c r="T4">
-        <v>0.7195887291652147</v>
+        <v>0.523889564079892</v>
       </c>
       <c r="U4">
-        <v>6765.8</v>
+        <v>6449.5</v>
       </c>
       <c r="V4">
-        <v>0.8440158678675682</v>
+        <v>0.7533142556794954</v>
       </c>
       <c r="W4">
-        <v>-0.07833165180746872</v>
+        <v>0.05854897790381661</v>
       </c>
       <c r="X4">
-        <v>0.102214755052536</v>
+        <v>0.08568169217428179</v>
       </c>
       <c r="Y4">
-        <v>-0.1805464068600047</v>
+        <v>-0.02713271427046517</v>
       </c>
       <c r="Z4">
-        <v>2.255142320714539</v>
+        <v>12.66003002438076</v>
       </c>
       <c r="AA4">
-        <v>0.1113806328758368</v>
+        <v>1.060689175191563</v>
       </c>
       <c r="AB4">
-        <v>0.0949109772334443</v>
+        <v>0.0812130828786954</v>
       </c>
       <c r="AC4">
-        <v>0.01646965564239247</v>
+        <v>0.9794760923128678</v>
       </c>
       <c r="AD4">
-        <v>1126.6</v>
+        <v>857</v>
       </c>
       <c r="AE4">
-        <v>0.2450856983451643</v>
+        <v>0.1875221793244182</v>
       </c>
       <c r="AF4">
-        <v>1126.845085698345</v>
+        <v>857.1875221793244</v>
       </c>
       <c r="AG4">
-        <v>-5638.954914301656</v>
+        <v>-5592.312477820676</v>
       </c>
       <c r="AH4">
-        <v>0.1232461477698463</v>
+        <v>0.09100923246055261</v>
       </c>
       <c r="AI4">
-        <v>0.1417656812638205</v>
+        <v>0.1005063815446586</v>
       </c>
       <c r="AJ4">
-        <v>-2.37205450469788</v>
+        <v>-1.883448733381457</v>
       </c>
       <c r="AK4">
-        <v>-4.767281009560479</v>
+        <v>-2.689662388873433</v>
       </c>
       <c r="AL4">
-        <v>12.2</v>
+        <v>10.4</v>
       </c>
       <c r="AM4">
-        <v>12.2</v>
+        <v>10.4</v>
       </c>
       <c r="AN4">
-        <v>1.42898637858626</v>
+        <v>0.4553206636949511</v>
       </c>
       <c r="AO4">
-        <v>52.81147540983606</v>
+        <v>167.375</v>
       </c>
       <c r="AP4">
-        <v>-7.15248514290708</v>
+        <v>-2.971173196022015</v>
       </c>
       <c r="AQ4">
-        <v>52.81147540983606</v>
+        <v>167.375</v>
       </c>
     </row>
     <row r="5">
@@ -984,124 +984,124 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0683</v>
+        <v>0.0548</v>
       </c>
       <c r="E5">
-        <v>0.05980000000000001</v>
+        <v>-0.0725</v>
       </c>
       <c r="F5">
-        <v>-0.0489</v>
+        <v>-0.0568</v>
       </c>
       <c r="G5">
-        <v>0.06084439843802051</v>
+        <v>0.1516655116803684</v>
       </c>
       <c r="H5">
-        <v>0.06084439843802051</v>
+        <v>0.1516655116803684</v>
       </c>
       <c r="I5">
-        <v>0.03678412611673629</v>
+        <v>0.07232937160459167</v>
       </c>
       <c r="J5">
-        <v>0.0318341148323688</v>
+        <v>0.05133103369876085</v>
       </c>
       <c r="K5">
-        <v>2343.6</v>
+        <v>1617.2</v>
       </c>
       <c r="L5">
-        <v>0.0380842188396306</v>
+        <v>0.02600246647190007</v>
       </c>
       <c r="M5">
-        <v>1352.7352</v>
+        <v>1366.7856</v>
       </c>
       <c r="N5">
-        <v>0.05814264714731495</v>
+        <v>0.06583650525281426</v>
       </c>
       <c r="O5">
-        <v>0.5772039597200888</v>
+        <v>0.8451555775414296</v>
       </c>
       <c r="P5">
-        <v>588.2352</v>
+        <v>563.3856</v>
       </c>
       <c r="Q5">
-        <v>0.02528325696945731</v>
+        <v>0.02713764251961677</v>
       </c>
       <c r="R5">
-        <v>0.2509964157706093</v>
+        <v>0.3483710116250309</v>
       </c>
       <c r="S5">
-        <v>764.5000000000001</v>
+        <v>803.4</v>
       </c>
       <c r="T5">
-        <v>0.5651512579845634</v>
+        <v>0.5878025053819707</v>
       </c>
       <c r="U5">
-        <v>13970.4</v>
+        <v>9901.200000000001</v>
       </c>
       <c r="V5">
-        <v>0.6004693584574784</v>
+        <v>0.4769295241398246</v>
       </c>
       <c r="W5">
-        <v>0.05242085202897059</v>
+        <v>0.07925663820903131</v>
       </c>
       <c r="X5">
-        <v>0.1084724837129108</v>
+        <v>0.09243527569871732</v>
       </c>
       <c r="Y5">
-        <v>-0.05605163168394023</v>
+        <v>-0.01317863748968601</v>
       </c>
       <c r="Z5">
-        <v>1.781447762118644</v>
+        <v>4.777730291786354</v>
       </c>
       <c r="AA5">
-        <v>0.05671081262715132</v>
+        <v>0.2452458346112759</v>
       </c>
       <c r="AB5">
-        <v>0.09402315486712791</v>
+        <v>0.0788251808446532</v>
       </c>
       <c r="AC5">
-        <v>-0.03731234223997659</v>
+        <v>0.1664206537666227</v>
       </c>
       <c r="AD5">
-        <v>6457.6</v>
+        <v>6562.8</v>
       </c>
       <c r="AE5">
-        <v>125.0209795828195</v>
+        <v>125.6991474343238</v>
       </c>
       <c r="AF5">
-        <v>6582.62097958282</v>
+        <v>6688.499147434324</v>
       </c>
       <c r="AG5">
-        <v>-7387.77902041718</v>
+        <v>-3212.700852565677</v>
       </c>
       <c r="AH5">
-        <v>0.2205349818700802</v>
+        <v>0.2436718310155841</v>
       </c>
       <c r="AI5">
-        <v>0.2439162218504418</v>
+        <v>0.2495382826937564</v>
       </c>
       <c r="AJ5">
-        <v>-0.4652833643384748</v>
+        <v>-0.1830849237877316</v>
       </c>
       <c r="AK5">
-        <v>-0.5675563205490096</v>
+        <v>-0.1900747835866665</v>
       </c>
       <c r="AL5">
-        <v>193.5</v>
+        <v>255.8</v>
       </c>
       <c r="AM5">
-        <v>193.5</v>
+        <v>255.8</v>
       </c>
       <c r="AN5">
-        <v>2.169746656810699</v>
+        <v>1.25529351007058</v>
       </c>
       <c r="AO5">
-        <v>11.71369509043928</v>
+        <v>17.59147771696638</v>
       </c>
       <c r="AP5">
-        <v>-2.482285807545588</v>
+        <v>-0.6145063890449067</v>
       </c>
       <c r="AQ5">
-        <v>11.71369509043928</v>
+        <v>17.59147771696638</v>
       </c>
     </row>
     <row r="6">
@@ -1121,124 +1121,124 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.09960000000000001</v>
+        <v>-0.0892</v>
       </c>
       <c r="E6">
-        <v>0.0527</v>
+        <v>-0.0394</v>
       </c>
       <c r="F6">
         <v>-0.09269999999999999</v>
       </c>
       <c r="G6">
-        <v>0.1343724210687517</v>
+        <v>0.1121974409457647</v>
       </c>
       <c r="H6">
-        <v>0.1343724210687517</v>
+        <v>0.1121974409457647</v>
       </c>
       <c r="I6">
-        <v>0.08502473654570604</v>
+        <v>0.1093936994362559</v>
       </c>
       <c r="J6">
-        <v>0.05425584061829693</v>
+        <v>0.090113532133048</v>
       </c>
       <c r="K6">
-        <v>869.6</v>
+        <v>667.9</v>
       </c>
       <c r="L6">
-        <v>0.03699197713099482</v>
+        <v>0.02995429939947886</v>
       </c>
       <c r="M6">
-        <v>396.6197999999999</v>
+        <v>328.8844</v>
       </c>
       <c r="N6">
-        <v>0.0583521847874062</v>
+        <v>0.04837104365219438</v>
       </c>
       <c r="O6">
-        <v>0.4560945262189511</v>
+        <v>0.4924156310824974</v>
       </c>
       <c r="P6">
-        <v>242.9198</v>
+        <v>238.4844</v>
       </c>
       <c r="Q6">
-        <v>0.03573926732381933</v>
+        <v>0.03507536180727144</v>
       </c>
       <c r="R6">
-        <v>0.2793465961361545</v>
+        <v>0.3570660278484803</v>
       </c>
       <c r="S6">
-        <v>153.7</v>
+        <v>90.40000000000003</v>
       </c>
       <c r="T6">
-        <v>0.3875247781376522</v>
+        <v>0.2748686164500354</v>
       </c>
       <c r="U6">
-        <v>8147.7</v>
+        <v>9247.9</v>
       </c>
       <c r="V6">
-        <v>1.198720023539797</v>
+        <v>1.360145311213084</v>
       </c>
       <c r="W6">
-        <v>0.0364058058384932</v>
+        <v>0.04430220217564341</v>
       </c>
       <c r="X6">
-        <v>0.3053379777792924</v>
+        <v>0.2041143375720059</v>
       </c>
       <c r="Y6">
-        <v>-0.2689321719407992</v>
+        <v>-0.1598121353963625</v>
       </c>
       <c r="Z6">
-        <v>0.4221379932990163</v>
+        <v>0.5681900517991491</v>
       </c>
       <c r="AA6">
-        <v>0.02290345168335912</v>
+        <v>0.05120161249048084</v>
       </c>
       <c r="AB6">
-        <v>0.08849393436760383</v>
+        <v>0.07012692387288674</v>
       </c>
       <c r="AC6">
-        <v>-0.06559048268424471</v>
+        <v>-0.01892531138240591</v>
       </c>
       <c r="AD6">
-        <v>32157.3</v>
+        <v>27000</v>
       </c>
       <c r="AE6">
-        <v>206.7774911542581</v>
+        <v>157.079327799854</v>
       </c>
       <c r="AF6">
-        <v>32364.07749115426</v>
+        <v>27157.07932779985</v>
       </c>
       <c r="AG6">
-        <v>24216.37749115426</v>
+        <v>17909.17932779985</v>
       </c>
       <c r="AH6">
-        <v>0.8264348063064579</v>
+        <v>0.7997660481478746</v>
       </c>
       <c r="AI6">
-        <v>0.6822096253360656</v>
+        <v>0.6020340059980918</v>
       </c>
       <c r="AJ6">
-        <v>0.7808365115363954</v>
+        <v>0.724822097402799</v>
       </c>
       <c r="AK6">
-        <v>0.616312349554465</v>
+        <v>0.4994057514184072</v>
       </c>
       <c r="AL6">
-        <v>14.7</v>
+        <v>38.9</v>
       </c>
       <c r="AM6">
-        <v>14.7</v>
+        <v>38.9</v>
       </c>
       <c r="AN6">
-        <v>13.69794683932527</v>
+        <v>9.866257399693049</v>
       </c>
       <c r="AO6">
-        <v>135.0952380952381</v>
+        <v>62.26478149100257</v>
       </c>
       <c r="AP6">
-        <v>10.31537633802788</v>
+        <v>6.544317520938336</v>
       </c>
       <c r="AQ6">
-        <v>135.0952380952381</v>
+        <v>62.26478149100257</v>
       </c>
     </row>
     <row r="7">
@@ -1258,34 +1258,34 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.177</v>
+        <v>0.17</v>
       </c>
       <c r="G7">
-        <v>-0.148640101201771</v>
+        <v>-0.1988826815642458</v>
       </c>
       <c r="H7">
-        <v>-0.148640101201771</v>
+        <v>-0.1988826815642458</v>
       </c>
       <c r="I7">
-        <v>-0.1846932321315623</v>
+        <v>0.0482122905027933</v>
       </c>
       <c r="J7">
-        <v>-0.1846932321315623</v>
+        <v>0.02410614525139665</v>
       </c>
       <c r="K7">
-        <v>-30.1</v>
+        <v>0.696</v>
       </c>
       <c r="L7">
-        <v>-0.1903858317520557</v>
+        <v>0.003888268156424581</v>
       </c>
       <c r="M7">
-        <v>0.456</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.0007332368547998071</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>-0.01514950166112957</v>
+        <v>-0</v>
       </c>
       <c r="P7">
         <v>-0</v>
@@ -1294,40 +1294,37 @@
         <v>-0</v>
       </c>
       <c r="R7">
+        <v>-0</v>
+      </c>
+      <c r="S7">
         <v>0</v>
       </c>
-      <c r="S7">
-        <v>0.456</v>
-      </c>
-      <c r="T7">
-        <v>1</v>
-      </c>
       <c r="U7">
-        <v>22.1</v>
+        <v>164.6</v>
       </c>
       <c r="V7">
-        <v>0.0355362598488503</v>
+        <v>0.2459653317393903</v>
       </c>
       <c r="W7">
-        <v>-0.1376944190301921</v>
+        <v>0.005399534522885958</v>
       </c>
       <c r="X7">
-        <v>0.09603567656368478</v>
+        <v>0.08263662167186504</v>
       </c>
       <c r="Y7">
-        <v>-0.2337300955938769</v>
+        <v>-0.07723708714897909</v>
       </c>
       <c r="Z7">
-        <v>0.8629912663755459</v>
+        <v>2.077988414343924</v>
       </c>
       <c r="AA7">
-        <v>-0.1593886462882096</v>
+        <v>0.05009229054689405</v>
       </c>
       <c r="AB7">
-        <v>0.09603567656368478</v>
+        <v>0.08263662167186504</v>
       </c>
       <c r="AC7">
-        <v>-0.2554243228518944</v>
+        <v>-0.03254433112497099</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1339,7 +1336,7 @@
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>-22.1</v>
+        <v>-164.6</v>
       </c>
       <c r="AH7">
         <v>0</v>
@@ -1348,10 +1345,10 @@
         <v>0</v>
       </c>
       <c r="AJ7">
-        <v>-0.03684561520506836</v>
+        <v>-0.3261989694807768</v>
       </c>
       <c r="AK7">
-        <v>-0.2069288389513108</v>
+        <v>-0.3935915829746534</v>
       </c>
       <c r="AL7">
         <v>0.007</v>
@@ -1360,16 +1357,16 @@
         <v>0.007</v>
       </c>
       <c r="AN7">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO7">
-        <v>-4171.428571428572</v>
+        <v>1232.857142857143</v>
       </c>
       <c r="AP7">
-        <v>0.8339622641509434</v>
+        <v>-13.83193277310924</v>
       </c>
       <c r="AQ7">
-        <v>-4171.428571428572</v>
+        <v>1232.857142857143</v>
       </c>
     </row>
   </sheetData>
